--- a/data/raw/clientes.xlsx
+++ b/data/raw/clientes.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>id_localidad</t>
+          <t>localidad_id</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>22533</v>
+        <v>22538</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         <v>103</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>44982</v>
+        <v>44987</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>17106</v>
+        <v>17111</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         <v>1004</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>44946</v>
+        <v>44951</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24903</v>
+        <v>24908</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>3017</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45493</v>
+        <v>45498</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>34584</v>
+        <v>34589</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v>2419</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45832</v>
+        <v>45837</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>22111</v>
+        <v>22116</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>123</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45367</v>
+        <v>45372</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>25647</v>
+        <v>25652</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>953</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45316</v>
+        <v>45321</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>33551</v>
+        <v>33556</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>2299</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45559</v>
+        <v>45564</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38229</v>
+        <v>38234</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>903</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45152</v>
+        <v>45157</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>35014</v>
+        <v>35019</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>3316</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>32042</v>
+        <v>32047</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>2860</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45326</v>
+        <v>45331</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>33355</v>
+        <v>33360</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1139</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45181</v>
+        <v>45186</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>22993</v>
+        <v>22998</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>3921</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45516</v>
+        <v>45521</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>39276</v>
+        <v>39281</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>380</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45307</v>
+        <v>45312</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>18575</v>
+        <v>18580</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>1471</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45790</v>
+        <v>45795</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>26964</v>
+        <v>26969</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>3306</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45979</v>
+        <v>45984</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>27668</v>
+        <v>27673</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>2197</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45850</v>
+        <v>45855</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>17910</v>
+        <v>17915</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>323</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>38378</v>
+        <v>38383</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>3398</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45486</v>
+        <v>45491</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>17793</v>
+        <v>17798</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>2365</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45322</v>
+        <v>45327</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>26932</v>
+        <v>26937</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>188</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45949</v>
+        <v>45954</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>35176</v>
+        <v>35181</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>3167</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45524</v>
+        <v>45529</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>23536</v>
+        <v>23541</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>3504</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45396</v>
+        <v>45401</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>29923</v>
+        <v>29928</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>1557</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45024</v>
+        <v>45029</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>18150</v>
+        <v>18155</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>2604</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45898</v>
+        <v>45903</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>29440</v>
+        <v>29445</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>1517</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45139</v>
+        <v>45144</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>35134</v>
+        <v>35139</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>2746</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45721</v>
+        <v>45726</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>38301</v>
+        <v>38306</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>2496</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45973</v>
+        <v>45978</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19021</v>
+        <v>19026</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>2188</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45875</v>
+        <v>45880</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>32211</v>
+        <v>32216</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>670</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45004</v>
+        <v>45009</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>22957</v>
+        <v>22962</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>1106</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45783</v>
+        <v>45788</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20127</v>
+        <v>20132</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>2805</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45972</v>
+        <v>45977</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>31873</v>
+        <v>31878</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>939</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45452</v>
+        <v>45457</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>37923</v>
+        <v>37928</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>1644</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45281</v>
+        <v>45286</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>24032</v>
+        <v>24037</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>865</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45445</v>
+        <v>45450</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>25174</v>
+        <v>25179</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>871</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45213</v>
+        <v>45218</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>19141</v>
+        <v>19146</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>1621</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45831</v>
+        <v>45836</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>16489</v>
+        <v>16494</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>586</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45044</v>
+        <v>45049</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>24249</v>
+        <v>24254</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>1011</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>32973</v>
+        <v>32978</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>3060</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45787</v>
+        <v>45792</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>27131</v>
+        <v>27136</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>3678</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45671</v>
+        <v>45676</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>20664</v>
+        <v>20669</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>1483</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45981</v>
+        <v>45986</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>17054</v>
+        <v>17059</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>2088</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45703</v>
+        <v>45708</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>16584</v>
+        <v>16589</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>3096</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45209</v>
+        <v>45214</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>17695</v>
+        <v>17700</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>627</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45861</v>
+        <v>45866</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>31674</v>
+        <v>31679</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>3245</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>23339</v>
+        <v>23344</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>2443</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45379</v>
+        <v>45384</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>18449</v>
+        <v>18454</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>1564</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45450</v>
+        <v>45455</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>37148</v>
+        <v>37153</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>2168</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>44945</v>
+        <v>44950</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>37659</v>
+        <v>37664</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>2787</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45276</v>
+        <v>45281</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>24801</v>
+        <v>24806</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>2793</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45902</v>
+        <v>45907</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>30475</v>
+        <v>30480</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>3149</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45014</v>
+        <v>45019</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>24570</v>
+        <v>24575</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>457</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>44966</v>
+        <v>44971</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>22020</v>
+        <v>22025</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>648</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45245</v>
+        <v>45250</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>19584</v>
+        <v>19589</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>3907</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45877</v>
+        <v>45882</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>35779</v>
+        <v>35784</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>3981</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45244</v>
+        <v>45249</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>22483</v>
+        <v>22488</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>2080</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45601</v>
+        <v>45606</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>24928</v>
+        <v>24933</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>3448</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45173</v>
+        <v>45178</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>23159</v>
+        <v>23164</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>2495</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45317</v>
+        <v>45322</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>22508</v>
+        <v>22513</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>1532</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45218</v>
+        <v>45223</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>24906</v>
+        <v>24911</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>2454</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45068</v>
+        <v>45073</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>35291</v>
+        <v>35296</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>80</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45280</v>
+        <v>45285</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>30901</v>
+        <v>30906</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>3600</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46027</v>
+        <v>46032</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>19445</v>
+        <v>19450</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>238</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45688</v>
+        <v>45693</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>31280</v>
+        <v>31285</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>351</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>44957</v>
+        <v>44962</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>17802</v>
+        <v>17807</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>3343</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45827</v>
+        <v>45832</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>21029</v>
+        <v>21034</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>526</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45051</v>
+        <v>45056</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>20155</v>
+        <v>20160</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>3879</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45747</v>
+        <v>45752</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>37826</v>
+        <v>37831</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>1086</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45907</v>
+        <v>45912</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>22408</v>
+        <v>22413</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>3951</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>44986</v>
+        <v>44991</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>37812</v>
+        <v>37817</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>2921</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45114</v>
+        <v>45119</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>36993</v>
+        <v>36998</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>4077</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45129</v>
+        <v>45134</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>23213</v>
+        <v>23218</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>1795</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>44976</v>
+        <v>44981</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>31040</v>
+        <v>31045</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>496</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45742</v>
+        <v>45747</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>30995</v>
+        <v>31000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>263</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45977</v>
+        <v>45982</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>33688</v>
+        <v>33693</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>2410</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45424</v>
+        <v>45429</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>37944</v>
+        <v>37949</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>2411</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45741</v>
+        <v>45746</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>27433</v>
+        <v>27438</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>291</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>31580</v>
+        <v>31585</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>938</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45285</v>
+        <v>45290</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>19366</v>
+        <v>19371</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>3522</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45669</v>
+        <v>45674</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>21184</v>
+        <v>21189</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>2106</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45580</v>
+        <v>45585</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>36841</v>
+        <v>36846</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>2741</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45452</v>
+        <v>45457</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>24444</v>
+        <v>24449</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>2209</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45430</v>
+        <v>45435</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>26043</v>
+        <v>26048</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>996</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45619</v>
+        <v>45624</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>34403</v>
+        <v>34408</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>780</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45904</v>
+        <v>45909</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>37632</v>
+        <v>37637</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>2700</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45895</v>
+        <v>45900</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>22101</v>
+        <v>22106</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>1735</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>44980</v>
+        <v>44985</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>25356</v>
+        <v>25361</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>3539</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45058</v>
+        <v>45063</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>22432</v>
+        <v>22437</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>2759</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>45971</v>
+        <v>45976</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>33289</v>
+        <v>33294</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>249</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>45405</v>
+        <v>45410</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>19097</v>
+        <v>19102</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>3280</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>44948</v>
+        <v>44953</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>17666</v>
+        <v>17671</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>785</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>45924</v>
+        <v>45929</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>35522</v>
+        <v>35527</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>575</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>18687</v>
+        <v>18692</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>1141</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>22834</v>
+        <v>22839</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>3582</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>45052</v>
+        <v>45057</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>34447</v>
+        <v>34452</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>3310</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45769</v>
+        <v>45774</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>33158</v>
+        <v>33163</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>208</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>45898</v>
+        <v>45903</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>21949</v>
+        <v>21954</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>3970</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45006</v>
+        <v>45011</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>19333</v>
+        <v>19338</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>682</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>45848</v>
+        <v>45853</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>32725</v>
+        <v>32730</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>1972</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>18916</v>
+        <v>18921</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>3697</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>45078</v>
+        <v>45083</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>16977</v>
+        <v>16982</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>1553</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>45846</v>
+        <v>45851</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>35694</v>
+        <v>35699</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>1087</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>45325</v>
+        <v>45330</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>19722</v>
+        <v>19727</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>1733</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>45017</v>
+        <v>45022</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>34980</v>
+        <v>34985</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>635</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>45280</v>
+        <v>45285</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>29407</v>
+        <v>29412</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>892</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>45598</v>
+        <v>45603</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>18273</v>
+        <v>18278</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>3064</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>45441</v>
+        <v>45446</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>27724</v>
+        <v>27729</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>206</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>45604</v>
+        <v>45609</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>37012</v>
+        <v>37017</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>2060</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>45173</v>
+        <v>45178</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>37120</v>
+        <v>37125</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>233</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>45448</v>
+        <v>45453</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>35095</v>
+        <v>35100</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>3488</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>45833</v>
+        <v>45838</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>22020</v>
+        <v>22025</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>2438</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>33223</v>
+        <v>33228</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>1654</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46027</v>
+        <v>46032</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>16598</v>
+        <v>16603</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>2372</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>45760</v>
+        <v>45765</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>20359</v>
+        <v>20364</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>2537</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>45180</v>
+        <v>45185</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>23210</v>
+        <v>23215</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>2693</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>33310</v>
+        <v>33315</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>3829</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>44947</v>
+        <v>44952</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>35440</v>
+        <v>35445</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>2744</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>45526</v>
+        <v>45531</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>37160</v>
+        <v>37165</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>978</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>45056</v>
+        <v>45061</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>26498</v>
+        <v>26503</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>537</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46007</v>
+        <v>46012</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>22494</v>
+        <v>22499</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>1873</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>45453</v>
+        <v>45458</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>19281</v>
+        <v>19286</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>39</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>45163</v>
+        <v>45168</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>35342</v>
+        <v>35347</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>301</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>45910</v>
+        <v>45915</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>27438</v>
+        <v>27443</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>2073</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>45418</v>
+        <v>45423</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>37118</v>
+        <v>37123</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>3823</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>45654</v>
+        <v>45659</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>38714</v>
+        <v>38719</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>3602</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>45032</v>
+        <v>45037</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>34201</v>
+        <v>34206</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>1168</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>45750</v>
+        <v>45755</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>39262</v>
+        <v>39267</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>3416</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>45448</v>
+        <v>45453</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>22710</v>
+        <v>22715</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>2506</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>45417</v>
+        <v>45422</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>19652</v>
+        <v>19657</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>2736</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>45081</v>
+        <v>45086</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>16900</v>
+        <v>16905</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>3817</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>45149</v>
+        <v>45154</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>29065</v>
+        <v>29070</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>3846</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>45175</v>
+        <v>45180</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>36555</v>
+        <v>36560</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>473</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>38915</v>
+        <v>38920</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>1116</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>45755</v>
+        <v>45760</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>36362</v>
+        <v>36367</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>2940</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>45737</v>
+        <v>45742</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>23227</v>
+        <v>23232</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>2816</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>44977</v>
+        <v>44982</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>22307</v>
+        <v>22312</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>2071</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>45162</v>
+        <v>45167</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>33747</v>
+        <v>33752</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>3709</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>45333</v>
+        <v>45338</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>31580</v>
+        <v>31585</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>2599</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>45306</v>
+        <v>45311</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>18008</v>
+        <v>18013</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>181</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>45159</v>
+        <v>45164</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>22426</v>
+        <v>22431</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>3159</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>45753</v>
+        <v>45758</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>30220</v>
+        <v>30225</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>662</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>45490</v>
+        <v>45495</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>32779</v>
+        <v>32784</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>2260</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>45461</v>
+        <v>45466</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>27995</v>
+        <v>28000</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>2298</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>45249</v>
+        <v>45254</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>24291</v>
+        <v>24296</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>309</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>45380</v>
+        <v>45385</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>24697</v>
+        <v>24702</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>2235</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>45706</v>
+        <v>45711</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>23076</v>
+        <v>23081</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>2386</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>24064</v>
+        <v>24069</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>1761</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>45483</v>
+        <v>45488</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>36119</v>
+        <v>36124</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>1263</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>45157</v>
+        <v>45162</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>17311</v>
+        <v>17316</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>3682</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>45990</v>
+        <v>45995</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>35413</v>
+        <v>35418</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>2794</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>44976</v>
+        <v>44981</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>39153</v>
+        <v>39158</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>1449</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>45246</v>
+        <v>45251</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>20738</v>
+        <v>20743</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>3989</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>45778</v>
+        <v>45783</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>34139</v>
+        <v>34144</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>3792</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>45151</v>
+        <v>45156</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>30217</v>
+        <v>30222</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>3999</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>45416</v>
+        <v>45421</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>29513</v>
+        <v>29518</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>102</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>38268</v>
+        <v>38273</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>3205</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>45717</v>
+        <v>45722</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>29324</v>
+        <v>29329</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>1093</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>45058</v>
+        <v>45063</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>23268</v>
+        <v>23273</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>1567</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>45201</v>
+        <v>45206</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>24838</v>
+        <v>24843</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>912</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>45824</v>
+        <v>45829</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>38543</v>
+        <v>38548</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>1433</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>45049</v>
+        <v>45054</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>28483</v>
+        <v>28488</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>914</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>45139</v>
+        <v>45144</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>24378</v>
+        <v>24383</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>1633</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>45386</v>
+        <v>45391</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>22617</v>
+        <v>22622</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>3541</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>45183</v>
+        <v>45188</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>38296</v>
+        <v>38301</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>1439</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>45011</v>
+        <v>45016</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>33162</v>
+        <v>33167</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>1638</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>17718</v>
+        <v>17723</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>3848</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>45790</v>
+        <v>45795</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>31634</v>
+        <v>31639</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>3593</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>45160</v>
+        <v>45165</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>17447</v>
+        <v>17452</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>2379</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>45153</v>
+        <v>45158</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>26213</v>
+        <v>26218</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>445</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>45810</v>
+        <v>45815</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>24680</v>
+        <v>24685</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>1416</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>22102</v>
+        <v>22107</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>1788</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>45993</v>
+        <v>45998</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>19178</v>
+        <v>19183</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>474</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>45715</v>
+        <v>45720</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>34526</v>
+        <v>34531</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>1044</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>45423</v>
+        <v>45428</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>24955</v>
+        <v>24960</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>7</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>45318</v>
+        <v>45323</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>35614</v>
+        <v>35619</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>1492</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>45360</v>
+        <v>45365</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>25884</v>
+        <v>25889</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>3887</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>45058</v>
+        <v>45063</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>35022</v>
+        <v>35027</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>2553</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>45105</v>
+        <v>45110</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>17708</v>
+        <v>17713</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>2949</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>45449</v>
+        <v>45454</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>16575</v>
+        <v>16580</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>1267</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>45382</v>
+        <v>45387</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>32659</v>
+        <v>32664</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>1337</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>44992</v>
+        <v>44997</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>21077</v>
+        <v>21082</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>2271</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>45818</v>
+        <v>45823</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>23519</v>
+        <v>23524</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>1723</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>45359</v>
+        <v>45364</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>34619</v>
+        <v>34624</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>2775</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>45818</v>
+        <v>45823</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>37726</v>
+        <v>37731</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>2522</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>45223</v>
+        <v>45228</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>16616</v>
+        <v>16621</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>1664</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>45342</v>
+        <v>45347</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>33044</v>
+        <v>33049</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>1245</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>45506</v>
+        <v>45511</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>28332</v>
+        <v>28337</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>1761</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>45967</v>
+        <v>45972</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>35206</v>
+        <v>35211</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>1905</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>45031</v>
+        <v>45036</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>30681</v>
+        <v>30686</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>2768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>45728</v>
+        <v>45733</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>29203</v>
+        <v>29208</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>1939</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>45331</v>
+        <v>45336</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>18262</v>
+        <v>18267</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>2699</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>44985</v>
+        <v>44990</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>35481</v>
+        <v>35486</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>2112</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>45519</v>
+        <v>45524</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>19752</v>
+        <v>19757</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>383</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>44941</v>
+        <v>44946</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>33186</v>
+        <v>33191</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>921</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>45364</v>
+        <v>45369</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>17247</v>
+        <v>17252</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>101</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>45092</v>
+        <v>45097</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>33927</v>
+        <v>33932</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>4031</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>45023</v>
+        <v>45028</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>36723</v>
+        <v>36728</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>1866</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>45158</v>
+        <v>45163</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>23915</v>
+        <v>23920</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>2943</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>45008</v>
+        <v>45013</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>25920</v>
+        <v>25925</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>2025</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>45771</v>
+        <v>45776</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>37761</v>
+        <v>37766</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>605</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>45144</v>
+        <v>45149</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>32520</v>
+        <v>32525</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>3657</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>45353</v>
+        <v>45358</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>38160</v>
+        <v>38165</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>897</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>45406</v>
+        <v>45411</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>34876</v>
+        <v>34881</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>1903</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>29710</v>
+        <v>29715</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>3758</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>45665</v>
+        <v>45670</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>25660</v>
+        <v>25665</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>547</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>45341</v>
+        <v>45346</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>26825</v>
+        <v>26830</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>3892</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>45952</v>
+        <v>45957</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>34431</v>
+        <v>34436</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>1748</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>45785</v>
+        <v>45790</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="F209" s="2" t="n">
-        <v>32399</v>
+        <v>32404</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>3675</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>45915</v>
+        <v>45920</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>21883</v>
+        <v>21888</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>1844</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>44960</v>
+        <v>44965</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>16862</v>
+        <v>16867</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>3441</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>45102</v>
+        <v>45107</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>21217</v>
+        <v>21222</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>3137</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>45566</v>
+        <v>45571</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>22060</v>
+        <v>22065</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>2568</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>45525</v>
+        <v>45530</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>16681</v>
+        <v>16686</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>1802</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>45002</v>
+        <v>45007</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>38507</v>
+        <v>38512</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>961</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>45214</v>
+        <v>45219</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>31037</v>
+        <v>31042</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>1310</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>19925</v>
+        <v>19930</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>567</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>45614</v>
+        <v>45619</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>35560</v>
+        <v>35565</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>1569</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>45698</v>
+        <v>45703</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>27180</v>
+        <v>27185</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>2894</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>35930</v>
+        <v>35935</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>1700</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>45626</v>
+        <v>45631</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>18616</v>
+        <v>18621</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>2223</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>45485</v>
+        <v>45490</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>37914</v>
+        <v>37919</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>256</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>46000</v>
+        <v>46005</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>23118</v>
+        <v>23123</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>1596</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>45496</v>
+        <v>45501</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>28770</v>
+        <v>28775</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>3510</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>45452</v>
+        <v>45457</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>27388</v>
+        <v>27393</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>1954</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>24256</v>
+        <v>24261</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>1224</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>45520</v>
+        <v>45525</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>19277</v>
+        <v>19282</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>2205</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>45653</v>
+        <v>45658</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>37108</v>
+        <v>37113</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>2000</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>45328</v>
+        <v>45333</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>18285</v>
+        <v>18290</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>1786</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>44993</v>
+        <v>44998</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>31206</v>
+        <v>31211</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>1593</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>45810</v>
+        <v>45815</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>35155</v>
+        <v>35160</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>2967</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>45729</v>
+        <v>45734</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>30744</v>
+        <v>30749</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>3767</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>44974</v>
+        <v>44979</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>19331</v>
+        <v>19336</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>3715</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>45686</v>
+        <v>45691</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>33765</v>
+        <v>33770</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>344</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>22509</v>
+        <v>22514</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>556</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>45914</v>
+        <v>45919</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>26279</v>
+        <v>26284</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>206</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>36548</v>
+        <v>36553</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>1341</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>45646</v>
+        <v>45651</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>29563</v>
+        <v>29568</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>1339</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>45482</v>
+        <v>45487</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>33994</v>
+        <v>33999</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>1140</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>45119</v>
+        <v>45124</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>33682</v>
+        <v>33687</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>3420</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>45923</v>
+        <v>45928</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>30239</v>
+        <v>30244</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>80</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>44950</v>
+        <v>44955</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>30405</v>
+        <v>30410</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>3900</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>45064</v>
+        <v>45069</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>23706</v>
+        <v>23711</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>2663</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>45789</v>
+        <v>45794</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>35712</v>
+        <v>35717</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>3090</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>45596</v>
+        <v>45601</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>23846</v>
+        <v>23851</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>817</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>45304</v>
+        <v>45309</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>25161</v>
+        <v>25166</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>978</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>45257</v>
+        <v>45262</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>23433</v>
+        <v>23438</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>2743</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>45991</v>
+        <v>45996</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>39283</v>
+        <v>39288</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>1905</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>45436</v>
+        <v>45441</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>26207</v>
+        <v>26212</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>3142</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>45920</v>
+        <v>45925</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>29262</v>
+        <v>29267</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>2482</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>45080</v>
+        <v>45085</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>33778</v>
+        <v>33783</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>3186</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>45353</v>
+        <v>45358</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>30811</v>
+        <v>30816</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>443</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>44961</v>
+        <v>44966</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>27793</v>
+        <v>27798</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>3805</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>45080</v>
+        <v>45085</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>32963</v>
+        <v>32968</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>1625</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>19745</v>
+        <v>19750</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>312</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>45592</v>
+        <v>45597</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>25968</v>
+        <v>25973</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>418</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>45142</v>
+        <v>45147</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>29632</v>
+        <v>29637</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>3483</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>45893</v>
+        <v>45898</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>38731</v>
+        <v>38736</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>3262</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>45320</v>
+        <v>45325</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>31384</v>
+        <v>31389</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>1423</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>45740</v>
+        <v>45745</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>23792</v>
+        <v>23797</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>2710</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>45927</v>
+        <v>45932</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>25422</v>
+        <v>25427</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>2073</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>45667</v>
+        <v>45672</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>31045</v>
+        <v>31050</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>52</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>45581</v>
+        <v>45586</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>29783</v>
+        <v>29788</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>433</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>45769</v>
+        <v>45774</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>33374</v>
+        <v>33379</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>2604</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>45069</v>
+        <v>45074</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>31579</v>
+        <v>31584</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>1784</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>45190</v>
+        <v>45195</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>35908</v>
+        <v>35913</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>2523</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>44981</v>
+        <v>44986</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>18034</v>
+        <v>18039</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>1905</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>45495</v>
+        <v>45500</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>25585</v>
+        <v>25590</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>1321</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>45004</v>
+        <v>45009</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>28172</v>
+        <v>28177</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>1143</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>45435</v>
+        <v>45440</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>23189</v>
+        <v>23194</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>3074</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>45737</v>
+        <v>45742</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>38244</v>
+        <v>38249</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>1378</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>44948</v>
+        <v>44953</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>34829</v>
+        <v>34834</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>3486</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>44945</v>
+        <v>44950</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>25057</v>
+        <v>25062</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>1998</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>45254</v>
+        <v>45259</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>17935</v>
+        <v>17940</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>3268</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>45577</v>
+        <v>45582</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>18557</v>
+        <v>18562</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>1146</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>45965</v>
+        <v>45970</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>37596</v>
+        <v>37601</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>2277</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>45298</v>
+        <v>45303</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>19155</v>
+        <v>19160</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>3884</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>45258</v>
+        <v>45263</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>18694</v>
+        <v>18699</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>989</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>29209</v>
+        <v>29214</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>2002</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>45799</v>
+        <v>45804</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>18979</v>
+        <v>18984</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>2829</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>45243</v>
+        <v>45248</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>32470</v>
+        <v>32475</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>1836</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>45939</v>
+        <v>45944</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>19492</v>
+        <v>19497</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>1206</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>45530</v>
+        <v>45535</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>39023</v>
+        <v>39028</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>2834</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>45711</v>
+        <v>45716</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>18627</v>
+        <v>18632</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>2720</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>44966</v>
+        <v>44971</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>28369</v>
+        <v>28374</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>1939</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>44976</v>
+        <v>44981</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>17903</v>
+        <v>17908</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>1743</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>45956</v>
+        <v>45961</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>17836</v>
+        <v>17841</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>1442</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>45303</v>
+        <v>45308</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>25364</v>
+        <v>25369</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>1110</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>45700</v>
+        <v>45705</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>18690</v>
+        <v>18695</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>945</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>45138</v>
+        <v>45143</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>17927</v>
+        <v>17932</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>1293</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>24812</v>
+        <v>24817</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>785</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>45206</v>
+        <v>45211</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>36007</v>
+        <v>36012</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>1133</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>45133</v>
+        <v>45138</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>30684</v>
+        <v>30689</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>4017</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>45929</v>
+        <v>45934</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>24678</v>
+        <v>24683</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>1214</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>18132</v>
+        <v>18137</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>735</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>45587</v>
+        <v>45592</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>38363</v>
+        <v>38368</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>2901</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>45050</v>
+        <v>45055</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>24368</v>
+        <v>24373</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>1124</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>45052</v>
+        <v>45057</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>24846</v>
+        <v>24851</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>2267</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>45180</v>
+        <v>45185</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>26619</v>
+        <v>26624</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>2613</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>45085</v>
+        <v>45090</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>20264</v>
+        <v>20269</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>3575</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>45086</v>
+        <v>45091</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>18483</v>
+        <v>18488</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>1923</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>45933</v>
+        <v>45938</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>25628</v>
+        <v>25633</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>1396</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>45170</v>
+        <v>45175</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>33053</v>
+        <v>33058</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>1035</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>45747</v>
+        <v>45752</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>30681</v>
+        <v>30686</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>3368</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>45823</v>
+        <v>45828</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>35267</v>
+        <v>35272</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>2015</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>45057</v>
+        <v>45062</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>20122</v>
+        <v>20127</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>622</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>29363</v>
+        <v>29368</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>349</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>45110</v>
+        <v>45115</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         </is>
       </c>
       <c r="F308" s="2" t="n">
-        <v>30929</v>
+        <v>30934</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>2286</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>45768</v>
+        <v>45773</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>25967</v>
+        <v>25972</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>3178</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>45159</v>
+        <v>45164</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>17410</v>
+        <v>17415</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>1846</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>45514</v>
+        <v>45519</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="F311" s="2" t="n">
-        <v>24175</v>
+        <v>24180</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>3524</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="F312" s="2" t="n">
-        <v>26805</v>
+        <v>26810</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>1251</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>45738</v>
+        <v>45743</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         </is>
       </c>
       <c r="F313" s="2" t="n">
-        <v>36119</v>
+        <v>36124</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>2498</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>45235</v>
+        <v>45240</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         </is>
       </c>
       <c r="F314" s="2" t="n">
-        <v>22648</v>
+        <v>22653</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>3882</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>45720</v>
+        <v>45725</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>17206</v>
+        <v>17211</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>1084</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>45479</v>
+        <v>45484</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>35062</v>
+        <v>35067</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>644</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>45941</v>
+        <v>45946</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="F317" s="2" t="n">
-        <v>26625</v>
+        <v>26630</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>2261</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>36457</v>
+        <v>36462</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>11</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>45649</v>
+        <v>45654</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         </is>
       </c>
       <c r="F319" s="2" t="n">
-        <v>29387</v>
+        <v>29392</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>2824</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>45941</v>
+        <v>45946</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>19133</v>
+        <v>19138</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>1193</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>45228</v>
+        <v>45233</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>36466</v>
+        <v>36471</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>1181</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>45395</v>
+        <v>45400</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>34758</v>
+        <v>34763</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>2880</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>45979</v>
+        <v>45984</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>37341</v>
+        <v>37346</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>2816</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>45804</v>
+        <v>45809</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="F324" s="2" t="n">
-        <v>38806</v>
+        <v>38811</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>3227</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>45450</v>
+        <v>45455</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>37604</v>
+        <v>37609</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>1742</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>45993</v>
+        <v>45998</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>38092</v>
+        <v>38097</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>2653</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>45427</v>
+        <v>45432</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>28565</v>
+        <v>28570</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>3386</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>45261</v>
+        <v>45266</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>28615</v>
+        <v>28620</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>245</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>45677</v>
+        <v>45682</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>34607</v>
+        <v>34612</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>2438</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>45909</v>
+        <v>45914</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>24204</v>
+        <v>24209</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>1799</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>45387</v>
+        <v>45392</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="F331" s="2" t="n">
-        <v>24843</v>
+        <v>24848</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>2821</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>45192</v>
+        <v>45197</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>16922</v>
+        <v>16927</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>3862</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>45198</v>
+        <v>45203</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>25772</v>
+        <v>25777</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>2212</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>45951</v>
+        <v>45956</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>26806</v>
+        <v>26811</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>330</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>45403</v>
+        <v>45408</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>23157</v>
+        <v>23162</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>3644</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>45113</v>
+        <v>45118</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>21411</v>
+        <v>21416</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>2473</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>44997</v>
+        <v>45002</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>28393</v>
+        <v>28398</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>375</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>45167</v>
+        <v>45172</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>34431</v>
+        <v>34436</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>3133</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>45657</v>
+        <v>45662</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>37629</v>
+        <v>37634</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>2361</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>44951</v>
+        <v>44956</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="F340" s="2" t="n">
-        <v>24615</v>
+        <v>24620</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>1928</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>45220</v>
+        <v>45225</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>23203</v>
+        <v>23208</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>3753</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>45183</v>
+        <v>45188</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="F342" s="2" t="n">
-        <v>36387</v>
+        <v>36392</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>4084</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>45686</v>
+        <v>45691</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>27400</v>
+        <v>27405</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>2601</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>45976</v>
+        <v>45981</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>33860</v>
+        <v>33865</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>1926</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>45166</v>
+        <v>45171</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>17803</v>
+        <v>17808</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>1366</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="F346" s="2" t="n">
-        <v>29046</v>
+        <v>29051</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>3514</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>45072</v>
+        <v>45077</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="F347" s="2" t="n">
-        <v>28809</v>
+        <v>28814</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>1687</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="F348" s="2" t="n">
-        <v>24017</v>
+        <v>24022</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>1181</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>45282</v>
+        <v>45287</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>31358</v>
+        <v>31363</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>3333</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>45466</v>
+        <v>45471</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         </is>
       </c>
       <c r="F350" s="2" t="n">
-        <v>30059</v>
+        <v>30064</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>1863</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>45331</v>
+        <v>45336</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>21805</v>
+        <v>21810</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>1034</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>19793</v>
+        <v>19798</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>3974</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>45725</v>
+        <v>45730</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         </is>
       </c>
       <c r="F353" s="2" t="n">
-        <v>30827</v>
+        <v>30832</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>3379</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>45533</v>
+        <v>45538</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         </is>
       </c>
       <c r="F354" s="2" t="n">
-        <v>35395</v>
+        <v>35400</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>1693</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>45871</v>
+        <v>45876</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         </is>
       </c>
       <c r="F355" s="2" t="n">
-        <v>37401</v>
+        <v>37406</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>2124</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>45261</v>
+        <v>45266</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="F356" s="2" t="n">
-        <v>39343</v>
+        <v>39348</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>2562</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>45115</v>
+        <v>45120</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         </is>
       </c>
       <c r="F357" s="2" t="n">
-        <v>30630</v>
+        <v>30635</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>834</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>44955</v>
+        <v>44960</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="F358" s="2" t="n">
-        <v>17765</v>
+        <v>17770</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>3800</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>45252</v>
+        <v>45257</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="F359" s="2" t="n">
-        <v>18994</v>
+        <v>18999</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>3608</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="F360" s="2" t="n">
-        <v>26079</v>
+        <v>26084</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>498</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>45326</v>
+        <v>45331</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="F361" s="2" t="n">
-        <v>37076</v>
+        <v>37081</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>2908</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>45392</v>
+        <v>45397</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="F362" s="2" t="n">
-        <v>21094</v>
+        <v>21099</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>2257</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>45346</v>
+        <v>45351</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         </is>
       </c>
       <c r="F363" s="2" t="n">
-        <v>16587</v>
+        <v>16592</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>382</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>45907</v>
+        <v>45912</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="F364" s="2" t="n">
-        <v>36080</v>
+        <v>36085</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>1891</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>45041</v>
+        <v>45046</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="F365" s="2" t="n">
-        <v>29795</v>
+        <v>29800</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>2042</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>45496</v>
+        <v>45501</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         </is>
       </c>
       <c r="F366" s="2" t="n">
-        <v>29632</v>
+        <v>29637</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>2085</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>45309</v>
+        <v>45314</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         </is>
       </c>
       <c r="F367" s="2" t="n">
-        <v>22507</v>
+        <v>22512</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>1702</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>45775</v>
+        <v>45780</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="F368" s="2" t="n">
-        <v>36880</v>
+        <v>36885</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>999</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>45433</v>
+        <v>45438</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         </is>
       </c>
       <c r="F369" s="2" t="n">
-        <v>35667</v>
+        <v>35672</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>1572</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>45097</v>
+        <v>45102</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="F370" s="2" t="n">
-        <v>35714</v>
+        <v>35719</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>3057</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>45451</v>
+        <v>45456</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="F371" s="2" t="n">
-        <v>36187</v>
+        <v>36192</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>1132</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>45538</v>
+        <v>45543</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         </is>
       </c>
       <c r="F372" s="2" t="n">
-        <v>16866</v>
+        <v>16871</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>3827</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         </is>
       </c>
       <c r="F373" s="2" t="n">
-        <v>19085</v>
+        <v>19090</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>3361</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>45549</v>
+        <v>45554</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="F374" s="2" t="n">
-        <v>29706</v>
+        <v>29711</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>2974</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>44953</v>
+        <v>44958</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="F375" s="2" t="n">
-        <v>17485</v>
+        <v>17490</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>3545</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>45470</v>
+        <v>45475</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="F376" s="2" t="n">
-        <v>19987</v>
+        <v>19992</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>2207</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>45788</v>
+        <v>45793</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="F377" s="2" t="n">
-        <v>33141</v>
+        <v>33146</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>1362</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>45378</v>
+        <v>45383</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         </is>
       </c>
       <c r="F378" s="2" t="n">
-        <v>28523</v>
+        <v>28528</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>1866</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>45601</v>
+        <v>45606</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         </is>
       </c>
       <c r="F379" s="2" t="n">
-        <v>34148</v>
+        <v>34153</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>4018</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="F380" s="2" t="n">
-        <v>19152</v>
+        <v>19157</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>2343</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>45909</v>
+        <v>45914</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="F381" s="2" t="n">
-        <v>37563</v>
+        <v>37568</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>3507</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>45792</v>
+        <v>45797</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         </is>
       </c>
       <c r="F382" s="2" t="n">
-        <v>28181</v>
+        <v>28186</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>1304</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>45657</v>
+        <v>45662</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="F383" s="2" t="n">
-        <v>28928</v>
+        <v>28933</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>2889</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>45815</v>
+        <v>45820</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="F384" s="2" t="n">
-        <v>34738</v>
+        <v>34743</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>4049</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>45033</v>
+        <v>45038</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         </is>
       </c>
       <c r="F385" s="2" t="n">
-        <v>21586</v>
+        <v>21591</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>2029</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>45943</v>
+        <v>45948</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="F386" s="2" t="n">
-        <v>32194</v>
+        <v>32199</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>2058</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>45951</v>
+        <v>45956</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="F387" s="2" t="n">
-        <v>29288</v>
+        <v>29293</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>3563</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>45684</v>
+        <v>45689</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         </is>
       </c>
       <c r="F388" s="2" t="n">
-        <v>27380</v>
+        <v>27385</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>409</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>45498</v>
+        <v>45503</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         </is>
       </c>
       <c r="F389" s="2" t="n">
-        <v>22172</v>
+        <v>22177</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>63</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>45853</v>
+        <v>45858</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="F390" s="2" t="n">
-        <v>22503</v>
+        <v>22508</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>1680</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>45824</v>
+        <v>45829</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         </is>
       </c>
       <c r="F391" s="2" t="n">
-        <v>29288</v>
+        <v>29293</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>307</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         </is>
       </c>
       <c r="F392" s="2" t="n">
-        <v>20686</v>
+        <v>20691</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>1387</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>45196</v>
+        <v>45201</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="F393" s="2" t="n">
-        <v>31273</v>
+        <v>31278</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>2662</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>45748</v>
+        <v>45753</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="F394" s="2" t="n">
-        <v>36990</v>
+        <v>36995</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>3492</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>45118</v>
+        <v>45123</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="F395" s="2" t="n">
-        <v>29851</v>
+        <v>29856</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>3909</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>45511</v>
+        <v>45516</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         </is>
       </c>
       <c r="F396" s="2" t="n">
-        <v>22150</v>
+        <v>22155</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>3574</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>45143</v>
+        <v>45148</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="F397" s="2" t="n">
-        <v>23487</v>
+        <v>23492</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>2530</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>45119</v>
+        <v>45124</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="F398" s="2" t="n">
-        <v>33541</v>
+        <v>33546</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>2586</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>45768</v>
+        <v>45773</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         </is>
       </c>
       <c r="F399" s="2" t="n">
-        <v>33363</v>
+        <v>33368</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>4086</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>45798</v>
+        <v>45803</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         </is>
       </c>
       <c r="F400" s="2" t="n">
-        <v>25006</v>
+        <v>25011</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>1778</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>45091</v>
+        <v>45096</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="F401" s="2" t="n">
-        <v>36352</v>
+        <v>36357</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>1818</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>45077</v>
+        <v>45082</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="F402" s="2" t="n">
-        <v>27268</v>
+        <v>27273</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>3701</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>45558</v>
+        <v>45563</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         </is>
       </c>
       <c r="F403" s="2" t="n">
-        <v>31297</v>
+        <v>31302</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>1329</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>45956</v>
+        <v>45961</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         </is>
       </c>
       <c r="F404" s="2" t="n">
-        <v>17282</v>
+        <v>17287</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>1469</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>45494</v>
+        <v>45499</v>
       </c>
       <c r="J404" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="F405" s="2" t="n">
-        <v>18605</v>
+        <v>18610</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>597</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>45076</v>
+        <v>45081</v>
       </c>
       <c r="J405" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         </is>
       </c>
       <c r="F406" s="2" t="n">
-        <v>39189</v>
+        <v>39194</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>2319</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>45563</v>
+        <v>45568</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="F407" s="2" t="n">
-        <v>29029</v>
+        <v>29034</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>697</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>45771</v>
+        <v>45776</v>
       </c>
       <c r="J407" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         </is>
       </c>
       <c r="F408" s="2" t="n">
-        <v>27452</v>
+        <v>27457</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>2497</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="J408" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         </is>
       </c>
       <c r="F409" s="2" t="n">
-        <v>28426</v>
+        <v>28431</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>2039</v>
       </c>
       <c r="I409" s="2" t="n">
-        <v>45484</v>
+        <v>45489</v>
       </c>
       <c r="J409" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         </is>
       </c>
       <c r="F410" s="2" t="n">
-        <v>22617</v>
+        <v>22622</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>952</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>45423</v>
+        <v>45428</v>
       </c>
       <c r="J410" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="F411" s="2" t="n">
-        <v>20990</v>
+        <v>20995</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>1883</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>45312</v>
+        <v>45317</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="F412" s="2" t="n">
-        <v>37199</v>
+        <v>37204</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>3682</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>45777</v>
+        <v>45782</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="F413" s="2" t="n">
-        <v>31873</v>
+        <v>31878</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>2776</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>45371</v>
+        <v>45376</v>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="F414" s="2" t="n">
-        <v>17792</v>
+        <v>17797</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>303</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="F415" s="2" t="n">
-        <v>33801</v>
+        <v>33806</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>4046</v>
       </c>
       <c r="I415" s="2" t="n">
-        <v>45838</v>
+        <v>45843</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="F416" s="2" t="n">
-        <v>21098</v>
+        <v>21103</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>2618</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>45594</v>
+        <v>45599</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="F417" s="2" t="n">
-        <v>25521</v>
+        <v>25526</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>1872</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>45355</v>
+        <v>45360</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="F418" s="2" t="n">
-        <v>21320</v>
+        <v>21325</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>1576</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>45712</v>
+        <v>45717</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         </is>
       </c>
       <c r="F419" s="2" t="n">
-        <v>29297</v>
+        <v>29302</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>972</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>45089</v>
+        <v>45094</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="F420" s="2" t="n">
-        <v>28291</v>
+        <v>28296</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>2355</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>45802</v>
+        <v>45807</v>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         </is>
       </c>
       <c r="F421" s="2" t="n">
-        <v>26681</v>
+        <v>26686</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>90</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>45487</v>
+        <v>45492</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         </is>
       </c>
       <c r="F422" s="2" t="n">
-        <v>27555</v>
+        <v>27560</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>1125</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>45591</v>
+        <v>45596</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         </is>
       </c>
       <c r="F423" s="2" t="n">
-        <v>18413</v>
+        <v>18418</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>3730</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="F424" s="2" t="n">
-        <v>31034</v>
+        <v>31039</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>3412</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>45300</v>
+        <v>45305</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="F425" s="2" t="n">
-        <v>35081</v>
+        <v>35086</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>2487</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>45019</v>
+        <v>45024</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="F426" s="2" t="n">
-        <v>19030</v>
+        <v>19035</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>2608</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>45377</v>
+        <v>45382</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="F427" s="2" t="n">
-        <v>37288</v>
+        <v>37293</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>2777</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>45359</v>
+        <v>45364</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         </is>
       </c>
       <c r="F428" s="2" t="n">
-        <v>29851</v>
+        <v>29856</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>2574</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>45684</v>
+        <v>45689</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         </is>
       </c>
       <c r="F429" s="2" t="n">
-        <v>24099</v>
+        <v>24104</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>1266</v>
       </c>
       <c r="I429" s="2" t="n">
-        <v>45470</v>
+        <v>45475</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         </is>
       </c>
       <c r="F430" s="2" t="n">
-        <v>39365</v>
+        <v>39370</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>2374</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>45863</v>
+        <v>45868</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         </is>
       </c>
       <c r="F431" s="2" t="n">
-        <v>21133</v>
+        <v>21138</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>370</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>45278</v>
+        <v>45283</v>
       </c>
       <c r="J431" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         </is>
       </c>
       <c r="F432" s="2" t="n">
-        <v>29287</v>
+        <v>29292</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>3062</v>
       </c>
       <c r="I432" s="2" t="n">
-        <v>45353</v>
+        <v>45358</v>
       </c>
       <c r="J432" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="F433" s="2" t="n">
-        <v>19842</v>
+        <v>19847</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>823</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>45434</v>
+        <v>45439</v>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="F434" s="2" t="n">
-        <v>16997</v>
+        <v>17002</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>2175</v>
       </c>
       <c r="I434" s="2" t="n">
-        <v>45297</v>
+        <v>45302</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="F435" s="2" t="n">
-        <v>24945</v>
+        <v>24950</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>3402</v>
       </c>
       <c r="I435" s="2" t="n">
-        <v>45162</v>
+        <v>45167</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="F436" s="2" t="n">
-        <v>29948</v>
+        <v>29953</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>3744</v>
       </c>
       <c r="I436" s="2" t="n">
-        <v>45322</v>
+        <v>45327</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         </is>
       </c>
       <c r="F437" s="2" t="n">
-        <v>34780</v>
+        <v>34785</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>3058</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         </is>
       </c>
       <c r="F438" s="2" t="n">
-        <v>32084</v>
+        <v>32089</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>1919</v>
       </c>
       <c r="I438" s="2" t="n">
-        <v>45244</v>
+        <v>45249</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         </is>
       </c>
       <c r="F439" s="2" t="n">
-        <v>21860</v>
+        <v>21865</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>3090</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>45550</v>
+        <v>45555</v>
       </c>
       <c r="J439" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="F440" s="2" t="n">
-        <v>30889</v>
+        <v>30894</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>3962</v>
       </c>
       <c r="I440" s="2" t="n">
-        <v>45180</v>
+        <v>45185</v>
       </c>
       <c r="J440" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         </is>
       </c>
       <c r="F441" s="2" t="n">
-        <v>35325</v>
+        <v>35330</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>370</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>45131</v>
+        <v>45136</v>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         </is>
       </c>
       <c r="F442" s="2" t="n">
-        <v>36046</v>
+        <v>36051</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>1084</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>45145</v>
+        <v>45150</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         </is>
       </c>
       <c r="F443" s="2" t="n">
-        <v>27321</v>
+        <v>27326</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>1863</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>45476</v>
+        <v>45481</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="F444" s="2" t="n">
-        <v>39176</v>
+        <v>39181</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>2395</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>45777</v>
+        <v>45782</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="F445" s="2" t="n">
-        <v>29022</v>
+        <v>29027</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>444</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>45034</v>
+        <v>45039</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         </is>
       </c>
       <c r="F446" s="2" t="n">
-        <v>21166</v>
+        <v>21171</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>1932</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>45572</v>
+        <v>45577</v>
       </c>
       <c r="J446" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         </is>
       </c>
       <c r="F447" s="2" t="n">
-        <v>32823</v>
+        <v>32828</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>3749</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>45102</v>
+        <v>45107</v>
       </c>
       <c r="J447" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="F448" s="2" t="n">
-        <v>32397</v>
+        <v>32402</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>2653</v>
       </c>
       <c r="I448" s="2" t="n">
-        <v>45505</v>
+        <v>45510</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         </is>
       </c>
       <c r="F449" s="2" t="n">
-        <v>39339</v>
+        <v>39344</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>3725</v>
       </c>
       <c r="I449" s="2" t="n">
-        <v>45582</v>
+        <v>45587</v>
       </c>
       <c r="J449" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="F450" s="2" t="n">
-        <v>36918</v>
+        <v>36923</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>2660</v>
       </c>
       <c r="I450" s="2" t="n">
-        <v>45271</v>
+        <v>45276</v>
       </c>
       <c r="J450" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="F451" s="2" t="n">
-        <v>22188</v>
+        <v>22193</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>573</v>
       </c>
       <c r="I451" s="2" t="n">
-        <v>45803</v>
+        <v>45808</v>
       </c>
       <c r="J451" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="F452" s="2" t="n">
-        <v>30777</v>
+        <v>30782</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>1247</v>
       </c>
       <c r="I452" s="2" t="n">
-        <v>45790</v>
+        <v>45795</v>
       </c>
       <c r="J452" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="F453" s="2" t="n">
-        <v>29717</v>
+        <v>29722</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>399</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>45438</v>
+        <v>45443</v>
       </c>
       <c r="J453" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="F454" s="2" t="n">
-        <v>25769</v>
+        <v>25774</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>1592</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>44936</v>
+        <v>44941</v>
       </c>
       <c r="J454" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         </is>
       </c>
       <c r="F455" s="2" t="n">
-        <v>16852</v>
+        <v>16857</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>2747</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>45425</v>
+        <v>45430</v>
       </c>
       <c r="J455" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="F456" s="2" t="n">
-        <v>36886</v>
+        <v>36891</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>2406</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>44994</v>
+        <v>44999</v>
       </c>
       <c r="J456" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         </is>
       </c>
       <c r="F457" s="2" t="n">
-        <v>25570</v>
+        <v>25575</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>3627</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>45055</v>
+        <v>45060</v>
       </c>
       <c r="J457" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="F458" s="2" t="n">
-        <v>28583</v>
+        <v>28588</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>3415</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>45831</v>
+        <v>45836</v>
       </c>
       <c r="J458" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         </is>
       </c>
       <c r="F459" s="2" t="n">
-        <v>25094</v>
+        <v>25099</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>3847</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>45020</v>
+        <v>45025</v>
       </c>
       <c r="J459" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         </is>
       </c>
       <c r="F460" s="2" t="n">
-        <v>30487</v>
+        <v>30492</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>2828</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>45860</v>
+        <v>45865</v>
       </c>
       <c r="J460" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         </is>
       </c>
       <c r="F461" s="2" t="n">
-        <v>23649</v>
+        <v>23654</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>1817</v>
       </c>
       <c r="I461" s="2" t="n">
-        <v>45556</v>
+        <v>45561</v>
       </c>
       <c r="J461" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="F462" s="2" t="n">
-        <v>35680</v>
+        <v>35685</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>3504</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="J462" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         </is>
       </c>
       <c r="F463" s="2" t="n">
-        <v>22469</v>
+        <v>22474</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>4018</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>45979</v>
+        <v>45984</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         </is>
       </c>
       <c r="F464" s="2" t="n">
-        <v>24418</v>
+        <v>24423</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>2231</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>45620</v>
+        <v>45625</v>
       </c>
       <c r="J464" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="F465" s="2" t="n">
-        <v>33481</v>
+        <v>33486</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>249</v>
       </c>
       <c r="I465" s="2" t="n">
-        <v>45900</v>
+        <v>45905</v>
       </c>
       <c r="J465" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         </is>
       </c>
       <c r="F466" s="2" t="n">
-        <v>16788</v>
+        <v>16793</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>778</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>45771</v>
+        <v>45776</v>
       </c>
       <c r="J466" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         </is>
       </c>
       <c r="F467" s="2" t="n">
-        <v>30087</v>
+        <v>30092</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>376</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>45003</v>
+        <v>45008</v>
       </c>
       <c r="J467" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         </is>
       </c>
       <c r="F468" s="2" t="n">
-        <v>36062</v>
+        <v>36067</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>2629</v>
       </c>
       <c r="I468" s="2" t="n">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="J468" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         </is>
       </c>
       <c r="F469" s="2" t="n">
-        <v>25400</v>
+        <v>25405</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>208</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>45090</v>
+        <v>45095</v>
       </c>
       <c r="J469" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         </is>
       </c>
       <c r="F470" s="2" t="n">
-        <v>29659</v>
+        <v>29664</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>4051</v>
       </c>
       <c r="I470" s="2" t="n">
-        <v>45758</v>
+        <v>45763</v>
       </c>
       <c r="J470" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="F471" s="2" t="n">
-        <v>20349</v>
+        <v>20354</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>282</v>
       </c>
       <c r="I471" s="2" t="n">
-        <v>45032</v>
+        <v>45037</v>
       </c>
       <c r="J471" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         </is>
       </c>
       <c r="F472" s="2" t="n">
-        <v>30240</v>
+        <v>30245</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>2402</v>
       </c>
       <c r="I472" s="2" t="n">
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         </is>
       </c>
       <c r="F473" s="2" t="n">
-        <v>26819</v>
+        <v>26824</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>1346</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>45257</v>
+        <v>45262</v>
       </c>
       <c r="J473" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         </is>
       </c>
       <c r="F474" s="2" t="n">
-        <v>36333</v>
+        <v>36338</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>1136</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>45041</v>
+        <v>45046</v>
       </c>
       <c r="J474" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="F475" s="2" t="n">
-        <v>21023</v>
+        <v>21028</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>2213</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>45574</v>
+        <v>45579</v>
       </c>
       <c r="J475" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="F476" s="2" t="n">
-        <v>34798</v>
+        <v>34803</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>451</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>45876</v>
+        <v>45881</v>
       </c>
       <c r="J476" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         </is>
       </c>
       <c r="F477" s="2" t="n">
-        <v>22186</v>
+        <v>22191</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>540</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>45221</v>
+        <v>45226</v>
       </c>
       <c r="J477" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="F478" s="2" t="n">
-        <v>20517</v>
+        <v>20522</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>3236</v>
       </c>
       <c r="I478" s="2" t="n">
-        <v>45038</v>
+        <v>45043</v>
       </c>
       <c r="J478" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         </is>
       </c>
       <c r="F479" s="2" t="n">
-        <v>37999</v>
+        <v>38004</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>65</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>45422</v>
+        <v>45427</v>
       </c>
       <c r="J479" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         </is>
       </c>
       <c r="F480" s="2" t="n">
-        <v>31206</v>
+        <v>31211</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>215</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>45001</v>
+        <v>45006</v>
       </c>
       <c r="J480" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         </is>
       </c>
       <c r="F481" s="2" t="n">
-        <v>26279</v>
+        <v>26284</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>2155</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>45409</v>
+        <v>45414</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="F482" s="2" t="n">
-        <v>26947</v>
+        <v>26952</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>1951</v>
       </c>
       <c r="I482" s="2" t="n">
-        <v>45076</v>
+        <v>45081</v>
       </c>
       <c r="J482" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         </is>
       </c>
       <c r="F483" s="2" t="n">
-        <v>38675</v>
+        <v>38680</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>2103</v>
       </c>
       <c r="I483" s="2" t="n">
-        <v>45853</v>
+        <v>45858</v>
       </c>
       <c r="J483" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         </is>
       </c>
       <c r="F484" s="2" t="n">
-        <v>18688</v>
+        <v>18693</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>1852</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>45113</v>
+        <v>45118</v>
       </c>
       <c r="J484" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="F485" s="2" t="n">
-        <v>29466</v>
+        <v>29471</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>3873</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>45527</v>
+        <v>45532</v>
       </c>
       <c r="J485" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         </is>
       </c>
       <c r="F486" s="2" t="n">
-        <v>30502</v>
+        <v>30507</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>2979</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>45416</v>
+        <v>45421</v>
       </c>
       <c r="J486" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         </is>
       </c>
       <c r="F487" s="2" t="n">
-        <v>32017</v>
+        <v>32022</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>1236</v>
       </c>
       <c r="I487" s="2" t="n">
-        <v>45648</v>
+        <v>45653</v>
       </c>
       <c r="J487" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         </is>
       </c>
       <c r="F488" s="2" t="n">
-        <v>31558</v>
+        <v>31563</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>250</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>45059</v>
+        <v>45064</v>
       </c>
       <c r="J488" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         </is>
       </c>
       <c r="F489" s="2" t="n">
-        <v>23359</v>
+        <v>23364</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>1747</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>45950</v>
+        <v>45955</v>
       </c>
       <c r="J489" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         </is>
       </c>
       <c r="F490" s="2" t="n">
-        <v>33025</v>
+        <v>33030</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>2009</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>45186</v>
+        <v>45191</v>
       </c>
       <c r="J490" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         </is>
       </c>
       <c r="F491" s="2" t="n">
-        <v>33841</v>
+        <v>33846</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>302</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>45400</v>
+        <v>45405</v>
       </c>
       <c r="J491" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         </is>
       </c>
       <c r="F492" s="2" t="n">
-        <v>35298</v>
+        <v>35303</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>2492</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>45754</v>
+        <v>45759</v>
       </c>
       <c r="J492" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="F493" s="2" t="n">
-        <v>31659</v>
+        <v>31664</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>517</v>
       </c>
       <c r="I493" s="2" t="n">
-        <v>45881</v>
+        <v>45886</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
       <c r="F494" s="2" t="n">
-        <v>31937</v>
+        <v>31942</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>1561</v>
       </c>
       <c r="I494" s="2" t="n">
-        <v>45882</v>
+        <v>45887</v>
       </c>
       <c r="J494" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         </is>
       </c>
       <c r="F495" s="2" t="n">
-        <v>16486</v>
+        <v>16491</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>1859</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>45006</v>
+        <v>45011</v>
       </c>
       <c r="J495" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         </is>
       </c>
       <c r="F496" s="2" t="n">
-        <v>21724</v>
+        <v>21729</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>407</v>
       </c>
       <c r="I496" s="2" t="n">
-        <v>45723</v>
+        <v>45728</v>
       </c>
       <c r="J496" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         </is>
       </c>
       <c r="F497" s="2" t="n">
-        <v>33493</v>
+        <v>33498</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>3494</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>45449</v>
+        <v>45454</v>
       </c>
       <c r="J497" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         </is>
       </c>
       <c r="F498" s="2" t="n">
-        <v>39218</v>
+        <v>39223</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>1762</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>45654</v>
+        <v>45659</v>
       </c>
       <c r="J498" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         </is>
       </c>
       <c r="F499" s="2" t="n">
-        <v>17839</v>
+        <v>17844</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>1695</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>45259</v>
+        <v>45264</v>
       </c>
       <c r="J499" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         </is>
       </c>
       <c r="F500" s="2" t="n">
-        <v>18092</v>
+        <v>18097</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>1634</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>45822</v>
+        <v>45827</v>
       </c>
       <c r="J500" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="F501" s="2" t="n">
-        <v>37936</v>
+        <v>37941</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>1281</v>
       </c>
       <c r="I501" s="2" t="n">
-        <v>45070</v>
+        <v>45075</v>
       </c>
       <c r="J501" t="inlineStr">
         <is>
